--- a/docs/downloads/20260902_Johor_Teduh_Weekly_Update.xlsx
+++ b/docs/downloads/20260902_Johor_Teduh_Weekly_Update.xlsx
@@ -1607,7 +1607,7 @@
         <v>45966</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>3692</v>
+        <v>4525</v>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
